--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:38</t>
+    <t xml:space="preserve">2026-09-10 00:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:46</t>
+    <t xml:space="preserve">2026-09-18 10:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:56</t>
+    <t xml:space="preserve">2026-09-23 14:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:15</t>
+    <t xml:space="preserve">2026-10-02 15:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_biobio.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Santa Juana</t>
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Cabrero</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Quilaco</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:30</t>
+    <t xml:space="preserve">2026-10-04 09:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:57</t>
+    <t xml:space="preserve">2026-10-05 14:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
